--- a/data/마진테이블.xlsx
+++ b/data/마진테이블.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3058" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3057" uniqueCount="665">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -34128,8 +34128,8 @@
       <c r="B599" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C599" s="1" t="s">
-        <v>549</v>
+      <c r="C599" s="1">
+        <v>79475749</v>
       </c>
       <c r="D599" s="1" t="s">
         <v>659</v>
